--- a/public/produits_import.xlsx
+++ b/public/produits_import.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,21 +422,18 @@
         <v>Unité</v>
       </c>
       <c r="H1" t="str">
-        <v>TVA %</v>
+        <v>Stock initial</v>
       </c>
       <c r="I1" t="str">
-        <v>Stock initial</v>
+        <v>Stock minimal</v>
       </c>
       <c r="J1" t="str">
-        <v>Stock minimal</v>
+        <v>Suivi de stock</v>
       </c>
       <c r="K1" t="str">
-        <v>Suivi de stock</v>
+        <v>Image du produit</v>
       </c>
       <c r="L1" t="str">
-        <v>Image du produit</v>
-      </c>
-      <c r="M1" t="str">
         <v>Variantes de prix</v>
       </c>
     </row>
@@ -463,21 +460,18 @@
         <v>bouteille</v>
       </c>
       <c r="H2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I2">
-        <v>24</v>
-      </c>
-      <c r="J2">
         <v>6</v>
       </c>
+      <c r="J2" t="str">
+        <v>oui</v>
+      </c>
       <c r="K2" t="str">
-        <v>oui</v>
+        <v>https://i.pinimg.com/1200x/9e/8b/6e/9e8b6ed6ee305de7e556f0480b7443b5.jpg</v>
       </c>
       <c r="L2" t="str">
-        <v>https://i.pinimg.com/1200x/9e/8b/6e/9e8b6ed6ee305de7e556f0480b7443b5.jpg</v>
-      </c>
-      <c r="M2" t="str">
         <v/>
       </c>
     </row>
@@ -504,21 +498,18 @@
         <v>sac</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>10</v>
-      </c>
-      <c r="J3">
         <v>2</v>
       </c>
+      <c r="J3" t="str">
+        <v>oui</v>
+      </c>
       <c r="K3" t="str">
-        <v>oui</v>
+        <v>https://i.pinimg.com/1200x/b6/65/7b/b6657b84bad3b9bdc3f78c7fe82c818a.jpg</v>
       </c>
       <c r="L3" t="str">
-        <v>https://i.pinimg.com/1200x/b6/65/7b/b6657b84bad3b9bdc3f78c7fe82c818a.jpg</v>
-      </c>
-      <c r="M3" t="str">
         <v/>
       </c>
     </row>
@@ -544,28 +535,25 @@
       <c r="G4" t="str">
         <v>pièce</v>
       </c>
-      <c r="H4">
-        <v>0</v>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4" t="str">
         <v/>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>non</v>
       </c>
       <c r="K4" t="str">
-        <v>non</v>
+        <v>https://i.pinimg.com/1200x/d4/3e/7a/d43e7ab23fdccec01c9b5e2dc18f2812.jpg</v>
       </c>
       <c r="L4" t="str">
-        <v>https://i.pinimg.com/1200x/d4/3e/7a/d43e7ab23fdccec01c9b5e2dc18f2812.jpg</v>
-      </c>
-      <c r="M4" t="str">
         <v>Petite:2500|Moyenne:4000|Grande:5500</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>